--- a/results/section5.2/dm_test_pinball_loss_results.xlsx
+++ b/results/section5.2/dm_test_pinball_loss_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ym_ya\Desktop\windpower\Simulation code and data\5.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ym_ya\Desktop\Simulation code and data\results\section5.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4F78D9-DF7A-46B2-87A8-4EAA3C0D054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF4F128-17BB-4342-8FE0-6BD9304C4D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="127" yWindow="0" windowWidth="23400" windowHeight="14880" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_Results" sheetId="1" r:id="rId1"/>
@@ -405,10 +405,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10683,7 +10679,7 @@
       <c r="F2">
         <v>-7.5810006936730119</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>4.7287887106911152E-14</v>
       </c>
       <c r="H2">
@@ -10727,7 +10723,7 @@
       <c r="F3">
         <v>-17.847957616919569</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>2.479156705575151E-67</v>
       </c>
       <c r="H3">
@@ -10771,7 +10767,7 @@
       <c r="F4">
         <v>-24.72850799580139</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>1.617871666961437E-121</v>
       </c>
       <c r="H4">
@@ -10815,7 +10811,7 @@
       <c r="F5">
         <v>-29.964714061875579</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>6.8342291166221456E-170</v>
       </c>
       <c r="H5">
@@ -10859,7 +10855,7 @@
       <c r="F6">
         <v>-33.636108278140732</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>1.721394112029471E-206</v>
       </c>
       <c r="H6">
@@ -10903,7 +10899,7 @@
       <c r="F7">
         <v>-36.40003011698829</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>3.8717284937565842E-235</v>
       </c>
       <c r="H7">
@@ -10947,7 +10943,7 @@
       <c r="F8">
         <v>-38.526284460414978</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>1.1176674176132409E-257</v>
       </c>
       <c r="H8">
@@ -10991,7 +10987,7 @@
       <c r="F9">
         <v>-40.295462513528648</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>1.0641642678125651E-276</v>
       </c>
       <c r="H9">
@@ -11035,7 +11031,7 @@
       <c r="F10">
         <v>-41.76251608603112</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>1.268508425131312E-292</v>
       </c>
       <c r="H10">
@@ -11079,7 +11075,7 @@
       <c r="F11">
         <v>-42.71044424839355</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>5.6656862290469418E-303</v>
       </c>
       <c r="H11">
@@ -11123,7 +11119,7 @@
       <c r="F12">
         <v>-43.117613425825468</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>1.9707144264075391E-307</v>
       </c>
       <c r="H12">
@@ -11167,7 +11163,7 @@
       <c r="F13">
         <v>-42.598560263812779</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>9.4866298263455846E-302</v>
       </c>
       <c r="H13">
@@ -11211,7 +11207,7 @@
       <c r="F14">
         <v>-41.683147988317828</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>9.286248121046804E-292</v>
       </c>
       <c r="H14">
@@ -11255,7 +11251,7 @@
       <c r="F15">
         <v>-40.769762802504331</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>7.8070152536097868E-282</v>
       </c>
       <c r="H15">
@@ -11299,7 +11295,7 @@
       <c r="F16">
         <v>-39.012472639864448</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>6.9668567383719781E-263</v>
       </c>
       <c r="H16">
@@ -11343,7 +11339,7 @@
       <c r="F17">
         <v>-38.152136209419403</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>1.101050964351767E-253</v>
       </c>
       <c r="H17">
@@ -11387,7 +11383,7 @@
       <c r="F18">
         <v>-38.789048531278723</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>1.726894454645979E-260</v>
       </c>
       <c r="H18">
@@ -11431,7 +11427,7 @@
       <c r="F19">
         <v>-36.110675324898331</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>4.2084309388920259E-232</v>
       </c>
       <c r="H19">
@@ -11475,7 +11471,7 @@
       <c r="F20">
         <v>-30.68866954033885</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>5.8835716948513151E-177</v>
       </c>
       <c r="H20">
@@ -11503,6 +11499,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12465,7 +12462,7 @@
       <c r="F2">
         <v>1.1868757189812511</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>0.23538424998059559</v>
       </c>
       <c r="H2">
@@ -12509,7 +12506,7 @@
       <c r="F3">
         <v>-3.5947334819542669</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>3.307154428997937E-4</v>
       </c>
       <c r="H3">
@@ -12553,7 +12550,7 @@
       <c r="F4">
         <v>-6.6857661990500068</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>2.7970866159325659E-11</v>
       </c>
       <c r="H4">
@@ -12597,7 +12594,7 @@
       <c r="F5">
         <v>-6.6103960523032868</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>4.6275106300244403E-11</v>
       </c>
       <c r="H5">
@@ -12641,7 +12638,7 @@
       <c r="F6">
         <v>-3.426006465424277</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>6.2196103472787604E-4</v>
       </c>
       <c r="H6">
@@ -12685,7 +12682,7 @@
       <c r="F7">
         <v>-2.2688751581340671</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>2.3356920988806502E-2</v>
       </c>
       <c r="H7">
@@ -12729,7 +12726,7 @@
       <c r="F8">
         <v>1.725625825314522</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>8.4532659360517015E-2</v>
       </c>
       <c r="H8">
@@ -12773,7 +12770,7 @@
       <c r="F9">
         <v>8.8375737603221651</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>1.756468587405265E-18</v>
       </c>
       <c r="H9">
@@ -12817,7 +12814,7 @@
       <c r="F10">
         <v>15.433419510489671</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>1.6818903412003819E-51</v>
       </c>
       <c r="H10">
@@ -12861,7 +12858,7 @@
       <c r="F11">
         <v>18.794961119832209</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>4.9603929521170903E-74</v>
       </c>
       <c r="H11">
@@ -12905,7 +12902,7 @@
       <c r="F12">
         <v>16.65202603644007</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>2.923786412902828E-59</v>
       </c>
       <c r="H12">
@@ -12949,7 +12946,7 @@
       <c r="F13">
         <v>7.5464393415350042</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>6.133832468230548E-14</v>
       </c>
       <c r="H13">
@@ -12993,7 +12990,7 @@
       <c r="F14">
         <v>-8.0069512173912081</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>1.750548274500802E-15</v>
       </c>
       <c r="H14">
@@ -13037,7 +13034,7 @@
       <c r="F15">
         <v>-18.494780436921829</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>7.0400698744241299E-72</v>
       </c>
       <c r="H15">
@@ -13081,7 +13078,7 @@
       <c r="F16">
         <v>-27.422134891106889</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>9.2144193830623056E-146</v>
       </c>
       <c r="H16">
@@ -13125,7 +13122,7 @@
       <c r="F17">
         <v>-39.798128971604328</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>2.4872771552545338E-271</v>
       </c>
       <c r="H17">
@@ -13169,7 +13166,7 @@
       <c r="F18">
         <v>-52.207587167100279</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18">
@@ -13213,7 +13210,7 @@
       <c r="F19">
         <v>-62.450575230912108</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19">
@@ -13257,7 +13254,7 @@
       <c r="F20">
         <v>-63.175161968618767</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>0</v>
       </c>
       <c r="H20">
